--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450764</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135450767</v>
+        <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99230</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1027,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brändåsen, Nb</t>
+          <t>Brändåsmyren, Nybyn NV Norrfjärden, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793995</v>
+        <v>793934</v>
       </c>
       <c r="R5" t="n">
-        <v>7276815</v>
+        <v>7276873</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1097,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>många blommande orkidéer, främst samlade kring en litet vattendrag i mossan, de flesta i full blom</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,24 +1126,295 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>boreal blandskog, kontinuitetsskog med inslag av sumpskog, inte tät, delvis strukturrik, hänglav, blåbärsskikt, gränsar till en myr/ mossmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135601047</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135450767</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brändåsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>793995</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7276815</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135450767</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135600731</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brändåsmyren, Nybyn NV Norrfjärden, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>793911</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7276902</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>växter som förekommer över relativt stora ytor, mycket fuktigt område, väldigt många i full blom</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>boreal blandsumpskog, kontinuitetsskog med inslag av sumpskog, inte tät, delvis strukturrik, hänglav, blåbärsskikt, gränsar till en mossmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600731</t>
         </is>
       </c>
     </row>
@@ -1132,6 +1424,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135450764</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135450766</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450765</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135450767</v>
       </c>
       <c r="B6" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135450764</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135450766</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450765</v>
       </c>
       <c r="B4" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135450767</v>
       </c>
       <c r="B6" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135450766</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450765</v>
       </c>
       <c r="B4" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135450767</v>
       </c>
       <c r="B6" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135450764</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135450766</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450765</v>
       </c>
       <c r="B4" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135450767</v>
       </c>
       <c r="B6" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30747-2026 artfynd.xlsx
+++ b/artfynd/A 30747-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135601047</v>
       </c>
       <c r="B5" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135600731</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
